--- a/AAII_Financials/Quarterly/ATHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>ATHR</t>
   </si>
@@ -656,76 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,7 +749,7 @@
         <v>300</v>
       </c>
       <c r="I8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3">
         <v>400</v>
@@ -765,8 +769,11 @@
       <c r="O8" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -821,7 +831,7 @@
         <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
@@ -836,7 +846,7 @@
         <v>200</v>
       </c>
       <c r="L10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>300</v>
@@ -847,8 +857,11 @@
       <c r="O10" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +892,8 @@
       <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -887,26 +901,29 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>700</v>
       </c>
       <c r="K17" s="3">
         <v>700</v>
       </c>
       <c r="L17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="M17" s="3">
         <v>500</v>
       </c>
       <c r="N17" s="3">
+        <v>500</v>
+      </c>
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-100</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
       <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1174,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1155,8 +1189,8 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
@@ -1182,54 +1216,60 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>100</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>8</v>
@@ -1264,49 +1304,55 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-100</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
       <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1316,14 +1362,14 @@
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>8</v>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-100</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
       <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1700,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1647,8 +1717,8 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
@@ -1674,49 +1744,55 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
-      </c>
-      <c r="K41" s="3">
-        <v>800</v>
       </c>
       <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="M41" s="3">
+        <v>800</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,16 +2049,19 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
@@ -2000,8 +2093,11 @@
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,8 +2137,11 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2058,11 +2157,11 @@
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -2071,10 +2170,10 @@
         <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
@@ -2082,49 +2181,55 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>700</v>
-      </c>
-      <c r="K46" s="3">
-        <v>900</v>
       </c>
       <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="M46" s="3">
+        <v>900</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,8 +2269,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2176,7 +2284,7 @@
         <v>1300</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
@@ -2196,17 +2304,20 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2217,7 +2328,7 @@
         <v>600</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -2246,8 +2357,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2339,14 +2459,14 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>900</v>
       </c>
       <c r="L54" s="3">
         <v>900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="M54" s="3">
+        <v>900</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O54" s="3">
         <v>100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,16 +2615,17 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -2506,28 +2637,31 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2544,22 +2678,22 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2567,8 +2701,11 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2597,42 +2734,45 @@
         <v>400</v>
       </c>
       <c r="L59" s="3">
+        <v>400</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E60" s="3">
         <v>600</v>
       </c>
       <c r="F60" s="3">
+        <v>600</v>
+      </c>
+      <c r="G60" s="3">
         <v>500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>600</v>
       </c>
       <c r="K60" s="3">
         <v>600</v>
@@ -2640,22 +2780,25 @@
       <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="M60" s="3">
+        <v>600</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2690,13 +2833,16 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,31 +3009,34 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>600</v>
+        <v>3600</v>
       </c>
       <c r="E66" s="3">
         <v>600</v>
       </c>
       <c r="F66" s="3">
+        <v>600</v>
+      </c>
+      <c r="G66" s="3">
         <v>500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>600</v>
       </c>
       <c r="K66" s="3">
         <v>600</v>
@@ -2886,17 +3044,20 @@
       <c r="L66" s="3">
         <v>600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="M66" s="3">
+        <v>600</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>-1100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>100</v>
-      </c>
-      <c r="K76" s="3">
-        <v>300</v>
       </c>
       <c r="L76" s="3">
         <v>300</v>
       </c>
       <c r="M76" s="3">
-        <v>-700</v>
+        <v>300</v>
       </c>
       <c r="N76" s="3">
         <v>-700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3624,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3461,14 +3660,17 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,34 +3886,37 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-1600</v>
       </c>
       <c r="G89" s="3">
         <v>-1600</v>
       </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-100</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
@@ -3708,13 +3925,16 @@
         <v>-100</v>
       </c>
       <c r="N89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3739,16 +3960,16 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,25 +4080,28 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3946,14 +4180,17 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>2800</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>7700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>100</v>
       </c>
       <c r="K100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>200</v>
       </c>
       <c r="M100" s="3">
+        <v>200</v>
+      </c>
+      <c r="N100" s="3">
         <v>700</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6000</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
       </c>
       <c r="I102" s="3">
         <v>-200</v>
       </c>
       <c r="J102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
     </row>
